--- a/outputs/final/kcnq1_primary_normal_vs_tumor/KCNQ1_primary_normal_vs_tumor_comparison.xlsx
+++ b/outputs/final/kcnq1_primary_normal_vs_tumor/KCNQ1_primary_normal_vs_tumor_comparison.xlsx
@@ -10,14 +10,16 @@
     <sheet name="Lauren_summary" sheetId="1" r:id="rId1"/>
     <sheet name="Lauren_cell_tests" sheetId="2" r:id="rId2"/>
     <sheet name="Lauren_patient" sheetId="3" r:id="rId3"/>
-    <sheet name="Lauren_patient_tests" sheetId="4" r:id="rId4"/>
+    <sheet name="Matched_pairs" sheetId="4" r:id="rId4"/>
+    <sheet name="Paired_normal_tumor" sheetId="5" r:id="rId5"/>
+    <sheet name="Lauren_patient_test" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>group</t>
   </si>
@@ -40,13 +42,13 @@
     <t>mean_raw_per_cell</t>
   </si>
   <si>
-    <t>mean_log1p_cpm</t>
+    <t>mean_log1p_cp10k</t>
   </si>
   <si>
     <t>mean_raw_among_detected</t>
   </si>
   <si>
-    <t>mean_log1p_cpm_among_detected</t>
+    <t>mean_log1p_cp10k_among_detected</t>
   </si>
   <si>
     <t>Primary normal epithelial</t>
@@ -70,7 +72,7 @@
     <t>fisher_p_detection</t>
   </si>
   <si>
-    <t>wilcoxon_p_log1p_cpm</t>
+    <t>wilcoxon_p_log1p_cp10k</t>
   </si>
   <si>
     <t>group_1_detection_pct</t>
@@ -79,16 +81,16 @@
     <t>group_2_detection_pct</t>
   </si>
   <si>
-    <t>group_1_mean_log1p_cpm</t>
-  </si>
-  <si>
-    <t>group_2_mean_log1p_cpm</t>
+    <t>group_1_mean_log1p_cp10k</t>
+  </si>
+  <si>
+    <t>group_2_mean_log1p_cp10k</t>
   </si>
   <si>
     <t>fisher_fdr_detection</t>
   </si>
   <si>
-    <t>wilcoxon_fdr_log1p_cpm</t>
+    <t>wilcoxon_fdr_log1p_cp10k</t>
   </si>
   <si>
     <t>Primary normal epithelial vs Tumor intestinal patient</t>
@@ -163,42 +165,110 @@
     <t>NGCII545</t>
   </si>
   <si>
-    <t>n_patients_group_1</t>
-  </si>
-  <si>
-    <t>n_patients_group_2</t>
-  </si>
-  <si>
-    <t>mannwhitney_p_detection_pct</t>
-  </si>
-  <si>
-    <t>mannwhitney_p_mean_log1p_cpm</t>
-  </si>
-  <si>
-    <t>median_detection_pct_group_1</t>
-  </si>
-  <si>
-    <t>median_detection_pct_group_2</t>
-  </si>
-  <si>
-    <t>median_mean_log1p_cpm_group_1</t>
-  </si>
-  <si>
-    <t>median_mean_log1p_cpm_group_2</t>
-  </si>
-  <si>
-    <t>fdr_detection_pct</t>
-  </si>
-  <si>
-    <t>fdr_mean_log1p_cpm</t>
+    <t>lauren</t>
+  </si>
+  <si>
+    <t>n_cells_normal</t>
+  </si>
+  <si>
+    <t>n_cells_tumor</t>
+  </si>
+  <si>
+    <t>detection_pct_normal</t>
+  </si>
+  <si>
+    <t>detection_pct_tumor</t>
+  </si>
+  <si>
+    <t>detection_difference_normal_minus_tumor</t>
+  </si>
+  <si>
+    <t>mean_log1p_cp10k_normal</t>
+  </si>
+  <si>
+    <t>mean_log1p_cp10k_tumor</t>
+  </si>
+  <si>
+    <t>mean_log1p_cp10k_difference_normal_minus_tumor</t>
+  </si>
+  <si>
+    <t>Intestinal</t>
+  </si>
+  <si>
+    <t>Diffuse</t>
+  </si>
+  <si>
+    <t>metric</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>n_pairs</t>
+  </si>
+  <si>
+    <t>statistic</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>median_normal</t>
+  </si>
+  <si>
+    <t>median_tumor</t>
+  </si>
+  <si>
+    <t>median_paired_difference_normal_minus_tumor</t>
+  </si>
+  <si>
+    <t>pairs_with_normal_higher</t>
+  </si>
+  <si>
+    <t>Matched primary normal epithelial vs primary tumor epithelial</t>
+  </si>
+  <si>
+    <t>KCNQ1 detection percentage</t>
+  </si>
+  <si>
+    <t>Mean KCNQ1 log1p(CP10K)</t>
+  </si>
+  <si>
+    <t>Exact paired Wilcoxon signed-rank</t>
+  </si>
+  <si>
+    <t>n_intestinal_patients</t>
+  </si>
+  <si>
+    <t>n_diffuse_patients</t>
+  </si>
+  <si>
+    <t>median_intestinal</t>
+  </si>
+  <si>
+    <t>median_diffuse</t>
+  </si>
+  <si>
+    <t>Tumor intestinal patients vs tumor diffuse patients</t>
+  </si>
+  <si>
+    <t>Two-sided Mann-Whitney U</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -214,7 +284,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -222,12 +292,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,34 +614,34 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -664,37 +752,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -814,28 +902,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1496,171 +1584,393 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2">
+        <v>1611</v>
+      </c>
+      <c r="D2">
+        <v>531</v>
+      </c>
+      <c r="E2">
+        <v>21.10490378646803</v>
+      </c>
+      <c r="F2">
+        <v>11.29943502824859</v>
+      </c>
+      <c r="G2">
+        <v>9.805468758219444</v>
+      </c>
+      <c r="H2">
+        <v>0.1582741167543348</v>
+      </c>
+      <c r="I2">
+        <v>0.08567648286722224</v>
+      </c>
+      <c r="J2">
+        <v>0.0725976338871126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3">
+        <v>780</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>16.41025641025641</v>
+      </c>
+      <c r="F3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G3">
+        <v>9.743589743589741</v>
+      </c>
+      <c r="H3">
+        <v>0.09806051178761992</v>
+      </c>
+      <c r="I3">
+        <v>0.01617376077929202</v>
+      </c>
+      <c r="J3">
+        <v>0.0818867510083279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4">
+        <v>1369</v>
+      </c>
+      <c r="D4">
+        <v>772</v>
+      </c>
+      <c r="E4">
+        <v>6.866325785244704</v>
+      </c>
+      <c r="F4">
+        <v>2.849740932642487</v>
+      </c>
+      <c r="G4">
+        <v>4.016584852602216</v>
+      </c>
+      <c r="H4">
+        <v>0.05932559396013519</v>
+      </c>
+      <c r="I4">
+        <v>0.02434530805831006</v>
+      </c>
+      <c r="J4">
+        <v>0.03498028590182513</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5">
+        <v>847</v>
+      </c>
+      <c r="D5">
+        <v>747</v>
+      </c>
+      <c r="E5">
+        <v>6.375442739079102</v>
+      </c>
+      <c r="F5">
+        <v>18.20615796519411</v>
+      </c>
+      <c r="G5">
+        <v>-11.83071522611501</v>
+      </c>
+      <c r="H5">
+        <v>0.04721025190415932</v>
+      </c>
+      <c r="I5">
+        <v>0.1137197293294544</v>
+      </c>
+      <c r="J5">
+        <v>-0.06650947742529506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6">
+        <v>422</v>
+      </c>
+      <c r="D6">
+        <v>732</v>
+      </c>
+      <c r="E6">
+        <v>23.69668246445498</v>
+      </c>
+      <c r="F6">
+        <v>16.80327868852459</v>
+      </c>
+      <c r="G6">
+        <v>6.893403775930388</v>
+      </c>
+      <c r="H6">
+        <v>0.1776195914043478</v>
+      </c>
+      <c r="I6">
+        <v>0.1149149935490143</v>
+      </c>
+      <c r="J6">
+        <v>0.06270459785533349</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0.1859305125558996</v>
+        <v>0.625</v>
       </c>
       <c r="G2">
-        <v>0.2192982456140351</v>
+        <v>16.41025641025641</v>
       </c>
       <c r="H2">
-        <v>16.41025641025641</v>
+        <v>11.29943502824859</v>
       </c>
       <c r="I2">
-        <v>6.776355880560635</v>
+        <v>6.893403775930388</v>
       </c>
       <c r="J2">
-        <v>0.09806051178761992</v>
-      </c>
-      <c r="K2">
-        <v>0.06019087104575409</v>
-      </c>
-      <c r="L2">
-        <v>0.2788957688338494</v>
-      </c>
-      <c r="M2">
-        <v>0.3289473684210527</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>0.3125</v>
+      </c>
+      <c r="G3">
+        <v>0.09806051178761992</v>
+      </c>
+      <c r="H3">
+        <v>0.08567648286722224</v>
+      </c>
+      <c r="I3">
+        <v>0.06270459785533349</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
         <v>6</v>
       </c>
+      <c r="F2">
+        <v>0.5466460268317854</v>
+      </c>
+      <c r="G2">
+        <v>6.776355880560635</v>
+      </c>
+      <c r="H2">
+        <v>6.325069483046137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
       <c r="F3">
-        <v>0.1774891774891775</v>
+        <v>0.4939628482972137</v>
       </c>
       <c r="G3">
-        <v>0.1255411255411255</v>
+        <v>0.06019087104575409</v>
       </c>
       <c r="H3">
-        <v>16.41025641025641</v>
-      </c>
-      <c r="I3">
-        <v>6.325069483046137</v>
-      </c>
-      <c r="J3">
-        <v>0.09806051178761992</v>
-      </c>
-      <c r="K3">
         <v>0.04601406633678844</v>
-      </c>
-      <c r="L3">
-        <v>0.2788957688338494</v>
-      </c>
-      <c r="M3">
-        <v>0.3289473684210527</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-      <c r="F4">
-        <v>0.5466460268317854</v>
-      </c>
-      <c r="G4">
-        <v>0.4939628482972137</v>
-      </c>
-      <c r="H4">
-        <v>6.776355880560635</v>
-      </c>
-      <c r="I4">
-        <v>6.325069483046137</v>
-      </c>
-      <c r="J4">
-        <v>0.06019087104575409</v>
-      </c>
-      <c r="K4">
-        <v>0.04601406633678844</v>
-      </c>
-      <c r="L4">
-        <v>0.5466460268317854</v>
-      </c>
-      <c r="M4">
-        <v>0.4939628482972137</v>
       </c>
     </row>
   </sheetData>
